--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohsen\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884D341A-7B64-4DAA-9A70-417C23FFEDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2089F0F7-74FC-43EB-B451-9DD2E18BA956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -495,9 +495,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,7 +505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -513,7 +513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -521,7 +521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -529,7 +529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -537,7 +537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -545,7 +545,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -553,7 +553,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -561,7 +561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -580,9 +580,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -605,7 +605,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -628,7 +628,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -651,7 +651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -674,7 +674,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -697,7 +697,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -720,7 +720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -743,7 +743,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -777,9 +777,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -802,7 +802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -825,7 +825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -848,7 +848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -871,7 +871,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -894,7 +894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -917,7 +917,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -940,7 +940,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -963,7 +963,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -986,7 +986,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1273,9 +1273,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1930,9 +1930,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2081,9 +2081,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2277,10 +2277,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2395,13 +2395,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
@@ -2409,9 +2418,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -2432,9 +2441,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -2455,9 +2464,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -2478,9 +2487,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
@@ -2501,9 +2510,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
@@ -2524,9 +2533,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
@@ -2547,9 +2556,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
@@ -2570,9 +2579,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
@@ -2593,9 +2602,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -2616,9 +2625,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -2639,9 +2648,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -2659,36 +2668,13 @@
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G5 A7:G18 C6:D6 F6:G6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G5 A6:G17" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2696,9 +2682,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2721,7 +2707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2744,7 +2730,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2767,7 +2753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2790,7 +2776,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2813,7 +2799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2836,7 +2822,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2859,7 +2845,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2882,7 +2868,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2905,7 +2891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2928,7 +2914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2951,7 +2937,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2974,7 +2960,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2997,7 +2983,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3020,7 +3006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3043,7 +3029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3066,7 +3052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3089,7 +3075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3112,7 +3098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3135,7 +3121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3158,7 +3144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3192,9 +3178,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -3217,7 +3203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3240,7 +3226,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3263,7 +3249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3286,7 +3272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3309,7 +3295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3332,7 +3318,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3355,7 +3341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3378,7 +3364,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3401,7 +3387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3424,7 +3410,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
